--- a/network/file/成绩登分册-6.xlsx
+++ b/network/file/成绩登分册-6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\network\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C3F8AE-8B2A-457D-8739-37659429461C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7ADCA0-9283-4493-8557-8B2DB54741D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7894F757-77BE-43E5-A7F7-5BED1F0CA09B}"/>
   </bookViews>
@@ -1302,6 +1302,39 @@
     <xf numFmtId="49" fontId="2" fillId="34" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1314,12 +1347,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1334,33 +1361,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1775,109 +1775,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48" t="s">
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48" t="s">
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
       <c r="M2" s="19"/>
     </row>
     <row r="3" spans="1:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
       <c r="L3" s="36" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="43"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="43" t="s">
+      <c r="A4" s="32"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="49" t="s">
+      <c r="H4" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="49" t="s">
+      <c r="I4" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="J4" s="49" t="s">
+      <c r="J4" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="K4" s="35"/>
+      <c r="K4" s="41"/>
       <c r="L4" s="36"/>
     </row>
     <row r="5" spans="1:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="43"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="35"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="41"/>
       <c r="L5" s="36"/>
       <c r="N5" s="27" t="s">
         <v>159</v>
@@ -2252,7 +2252,7 @@
       <c r="I18" s="10">
         <v>10</v>
       </c>
-      <c r="J18" s="50">
+      <c r="J18" s="31">
         <v>0</v>
       </c>
       <c r="K18" s="10"/>
@@ -2422,7 +2422,7 @@
       <c r="I24" s="10">
         <v>12</v>
       </c>
-      <c r="J24" s="50">
+      <c r="J24" s="31">
         <v>0</v>
       </c>
       <c r="K24" s="10"/>
@@ -2508,7 +2508,7 @@
       <c r="I27" s="10">
         <v>6</v>
       </c>
-      <c r="J27" s="50">
+      <c r="J27" s="31">
         <v>0</v>
       </c>
       <c r="K27" s="10"/>
@@ -2622,7 +2622,7 @@
       <c r="I31" s="10">
         <v>0</v>
       </c>
-      <c r="J31" s="50">
+      <c r="J31" s="31">
         <v>0</v>
       </c>
       <c r="K31" s="10"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="D44" s="10"/>
       <c r="E44" s="10">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="10">
@@ -3112,7 +3112,7 @@
       <c r="I48" s="10">
         <v>1</v>
       </c>
-      <c r="J48" s="50">
+      <c r="J48" s="31">
         <v>0</v>
       </c>
       <c r="K48" s="10"/>
@@ -3140,103 +3140,103 @@
     </row>
     <row r="50" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="51" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="46" t="s">
+      <c r="A51" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B51" s="46"/>
-      <c r="C51" s="46"/>
-      <c r="D51" s="46"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="46"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="46"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="46"/>
-      <c r="M51" s="46"/>
+      <c r="B51" s="33"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="33"/>
+      <c r="G51" s="33"/>
+      <c r="H51" s="33"/>
+      <c r="I51" s="33"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="33"/>
+      <c r="M51" s="33"/>
     </row>
     <row r="52" spans="1:13" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="47" t="s">
+      <c r="A52" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B52" s="47"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="48" t="s">
+      <c r="B52" s="34"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="E52" s="48"/>
-      <c r="F52" s="48"/>
-      <c r="G52" s="48" t="s">
+      <c r="E52" s="35"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="H52" s="48"/>
-      <c r="I52" s="48"/>
-      <c r="J52" s="48" t="s">
+      <c r="H52" s="35"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="K52" s="48"/>
-      <c r="L52" s="48"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="35"/>
       <c r="M52" s="19"/>
     </row>
     <row r="53" spans="1:13" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="43" t="s">
+      <c r="A53" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B53" s="44" t="s">
+      <c r="B53" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="45" t="s">
+      <c r="C53" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="D53" s="42" t="s">
+      <c r="D53" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="E53" s="42"/>
-      <c r="F53" s="42"/>
-      <c r="G53" s="42"/>
-      <c r="H53" s="42"/>
-      <c r="I53" s="42"/>
-      <c r="J53" s="42"/>
-      <c r="K53" s="42"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="38"/>
+      <c r="I53" s="38"/>
+      <c r="J53" s="38"/>
+      <c r="K53" s="38"/>
       <c r="L53" s="36" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:13" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="43"/>
-      <c r="B54" s="44"/>
-      <c r="C54" s="45"/>
-      <c r="D54" s="35" t="s">
+      <c r="A54" s="32"/>
+      <c r="B54" s="39"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="E54" s="35" t="s">
+      <c r="E54" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="F54" s="35" t="s">
+      <c r="F54" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="G54" s="35" t="s">
+      <c r="G54" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="H54" s="35"/>
-      <c r="I54" s="35"/>
-      <c r="J54" s="35"/>
-      <c r="K54" s="35"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="41"/>
+      <c r="J54" s="41"/>
+      <c r="K54" s="41"/>
       <c r="L54" s="36"/>
     </row>
     <row r="55" spans="1:13" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="43"/>
-      <c r="B55" s="44"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="35"/>
-      <c r="H55" s="35"/>
-      <c r="I55" s="35"/>
-      <c r="J55" s="35"/>
-      <c r="K55" s="35"/>
+      <c r="A55" s="32"/>
+      <c r="B55" s="39"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="41"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="41"/>
+      <c r="J55" s="41"/>
+      <c r="K55" s="41"/>
       <c r="L55" s="36"/>
     </row>
     <row r="56" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -3264,27 +3264,27 @@
       <c r="C57" s="12"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A58" s="37" t="s">
+      <c r="A58" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="37"/>
-      <c r="I58" s="37"/>
-      <c r="J58" s="37"/>
-      <c r="K58" s="37"/>
-      <c r="L58" s="37"/>
+      <c r="B58" s="46"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="46"/>
+      <c r="I58" s="46"/>
+      <c r="J58" s="46"/>
+      <c r="K58" s="46"/>
+      <c r="L58" s="46"/>
       <c r="M58" s="20"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A59" s="38" t="s">
+      <c r="A59" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B59" s="39"/>
+      <c r="B59" s="48"/>
       <c r="C59" s="6" t="s">
         <v>12</v>
       </c>
@@ -3300,30 +3300,30 @@
       <c r="G59" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H59" s="38" t="s">
+      <c r="H59" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="I59" s="40"/>
-      <c r="J59" s="39"/>
-      <c r="K59" s="41" t="s">
+      <c r="I59" s="49"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="L59" s="41"/>
+      <c r="L59" s="50"/>
       <c r="M59" s="21"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A60" s="31"/>
-      <c r="B60" s="31"/>
+      <c r="A60" s="42"/>
+      <c r="B60" s="42"/>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
       <c r="E60" s="13"/>
       <c r="F60" s="14"/>
       <c r="G60" s="14"/>
-      <c r="H60" s="32"/>
-      <c r="I60" s="33"/>
-      <c r="J60" s="34"/>
-      <c r="K60" s="31"/>
-      <c r="L60" s="31"/>
+      <c r="H60" s="43"/>
+      <c r="I60" s="44"/>
+      <c r="J60" s="45"/>
+      <c r="K60" s="42"/>
+      <c r="L60" s="42"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B61" s="24"/>
@@ -3347,32 +3347,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="A51:M51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="J52:L52"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D3:K3"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="H60:J60"/>
@@ -3389,7 +3363,33 @@
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="C53:C55"/>
     <mergeCell ref="D54:D55"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
     <mergeCell ref="E54:E55"/>
+    <mergeCell ref="A51:M51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D3:K3"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.10972222222222222" right="0.10972222222222222" top="0.38124999999999998" bottom="0.5" header="0.38124999999999998" footer="0.5"/>

--- a/network/file/成绩登分册-6.xlsx
+++ b/network/file/成绩登分册-6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\network\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7ADCA0-9283-4493-8557-8B2DB54741D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A70B27-B48B-49C1-BBA4-14268037AC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7894F757-77BE-43E5-A7F7-5BED1F0CA09B}"/>
   </bookViews>
@@ -17,12 +17,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="167">
   <si>
     <t>广州华立学院学生平时成绩登记表</t>
   </si>
@@ -499,10 +499,6 @@
   </si>
   <si>
     <t>5123210102087</t>
-  </si>
-  <si>
-    <t>平均签到率</t>
-    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>郑宇哲</t>
@@ -513,11 +509,27 @@
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
-    <t>其它活动</t>
+    <t>考试</t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
-    <t>考试</t>
+    <t>考试成绩</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>全勤</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>其它</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终成绩</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>平时累计</t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
@@ -525,7 +537,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -699,8 +711,30 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="8"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -890,18 +924,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1234,7 +1256,7 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1293,74 +1315,113 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="34" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1408,7 +1469,17 @@
     <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="注释" xfId="1" builtinId="10" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1482,13 +1553,13 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStylePreset3_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{42DFC6CA-D39A-4957-982A-AA333012E1C3}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1763,160 +1834,207 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
     <col min="2" max="2" width="11.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="11.625" style="5" customWidth="1"/>
-    <col min="4" max="11" width="7.25" customWidth="1"/>
+    <col min="4" max="11" width="7.25" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="7.875" customWidth="1"/>
-    <col min="13" max="13" width="5" customWidth="1"/>
+    <col min="13" max="15" width="7.875" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="8" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-    </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="34" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+    </row>
+    <row r="2" spans="1:18" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="35" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35" t="s">
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35" t="s">
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="19"/>
-    </row>
-    <row r="3" spans="1:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="32" t="s">
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="19"/>
+    </row>
+    <row r="3" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="36" t="s">
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="50" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="32"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="32" t="s">
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+    </row>
+    <row r="4" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="57"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60" t="s">
+        <v>160</v>
+      </c>
+      <c r="K4" s="60" t="s">
+        <v>163</v>
+      </c>
+      <c r="L4" s="50"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="Q4" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="57"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="O5" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="P5" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q5" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="J4" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="K4" s="41"/>
-      <c r="L4" s="36"/>
-    </row>
-    <row r="5" spans="1:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="32"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="36"/>
-      <c r="N5" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="O5" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R5" s="27" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="31" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>27</v>
       </c>
       <c r="D6" s="10"/>
-      <c r="E6" s="10">
+      <c r="E6" s="34">
         <v>44</v>
       </c>
-      <c r="F6" s="10"/>
+      <c r="F6" s="10">
+        <v>97</v>
+      </c>
       <c r="G6" s="10">
-        <v>81</v>
-      </c>
-      <c r="H6" s="10">
+        <v>100</v>
+      </c>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10">
         <v>2</v>
       </c>
-      <c r="I6" s="10">
+      <c r="K6" s="10"/>
+      <c r="L6" s="10">
+        <v>83.7</v>
+      </c>
+      <c r="M6" s="2">
+        <f>E6*0.3+F6*0.5+G6*0.2+J6+K6</f>
+        <v>83.7</v>
+      </c>
+      <c r="N6" s="2">
         <v>16</v>
       </c>
-      <c r="J6" s="10">
+      <c r="O6" s="2">
         <v>95</v>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-    </row>
-    <row r="7" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P6" s="2">
+        <f>N6+O6</f>
+        <v>111</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>69.5</v>
+      </c>
+      <c r="R6" s="2">
+        <f>L6*0.3+Q6*0.7</f>
+        <v>73.759999999999991</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
         <v>28</v>
       </c>
@@ -1930,21 +2048,42 @@
       <c r="E7" s="10">
         <v>89</v>
       </c>
-      <c r="F7" s="10"/>
+      <c r="F7" s="10">
+        <v>85</v>
+      </c>
       <c r="G7" s="10">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H7" s="10"/>
-      <c r="I7" s="10">
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10">
+        <v>86.2</v>
+      </c>
+      <c r="M7" s="2">
+        <f t="shared" ref="M7:M48" si="0">E7*0.3+F7*0.5+G7*0.2+J7+K7</f>
+        <v>86.2</v>
+      </c>
+      <c r="N7" s="2">
         <v>28</v>
       </c>
-      <c r="J7" s="10">
+      <c r="O7" s="2">
         <v>57</v>
       </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-    </row>
-    <row r="8" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P7" s="2">
+        <f t="shared" ref="P7:P48" si="1">N7+O7</f>
+        <v>85</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>64</v>
+      </c>
+      <c r="R7" s="2">
+        <f t="shared" ref="R7:R56" si="2">L7*0.3+Q7*0.7</f>
+        <v>70.66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
         <v>31</v>
       </c>
@@ -1958,51 +2097,95 @@
       <c r="E8" s="10">
         <v>100</v>
       </c>
-      <c r="F8" s="10"/>
+      <c r="F8" s="10">
+        <v>88</v>
+      </c>
       <c r="G8" s="10">
-        <v>81</v>
-      </c>
-      <c r="H8" s="10">
+        <v>95</v>
+      </c>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10">
         <v>1</v>
       </c>
-      <c r="I8" s="10">
+      <c r="K8" s="10">
+        <v>5</v>
+      </c>
+      <c r="L8" s="10">
+        <v>99</v>
+      </c>
+      <c r="M8" s="2">
+        <f t="shared" si="0"/>
+        <v>99</v>
+      </c>
+      <c r="N8" s="2">
         <v>0</v>
       </c>
-      <c r="J8" s="10">
+      <c r="O8" s="2">
         <v>95</v>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-    </row>
-    <row r="9" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P8" s="2">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>80.5</v>
+      </c>
+      <c r="R8" s="2">
+        <f t="shared" si="2"/>
+        <v>86.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="31" t="s">
         <v>35</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>36</v>
       </c>
       <c r="D9" s="10"/>
-      <c r="E9" s="10">
+      <c r="E9" s="34">
         <v>33</v>
       </c>
-      <c r="F9" s="10"/>
+      <c r="F9" s="10">
+        <v>83</v>
+      </c>
       <c r="G9" s="10">
         <v>81</v>
       </c>
       <c r="H9" s="10"/>
-      <c r="I9" s="10">
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="M9" s="2">
+        <f t="shared" si="0"/>
+        <v>67.599999999999994</v>
+      </c>
+      <c r="N9" s="2">
         <v>-2</v>
       </c>
-      <c r="J9" s="10">
+      <c r="O9" s="2">
         <v>0</v>
       </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-    </row>
-    <row r="10" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P9" s="2">
+        <f t="shared" si="1"/>
+        <v>-2</v>
+      </c>
+      <c r="Q9" s="33">
+        <v>43.5</v>
+      </c>
+      <c r="R9" s="2">
+        <f t="shared" si="2"/>
+        <v>50.73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
@@ -2016,21 +2199,44 @@
       <c r="E10" s="10">
         <v>100</v>
       </c>
-      <c r="F10" s="10"/>
+      <c r="F10" s="10">
+        <v>100</v>
+      </c>
       <c r="G10" s="10">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="H10" s="10"/>
-      <c r="I10" s="10">
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10">
+        <v>5</v>
+      </c>
+      <c r="L10" s="10">
+        <v>100</v>
+      </c>
+      <c r="M10" s="2">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="N10" s="2">
         <v>58</v>
       </c>
-      <c r="J10" s="10">
+      <c r="O10" s="2">
         <v>95</v>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-    </row>
-    <row r="11" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P10" s="2">
+        <f t="shared" si="1"/>
+        <v>153</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>61</v>
+      </c>
+      <c r="R10" s="2">
+        <f t="shared" si="2"/>
+        <v>72.699999999999989</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
         <v>40</v>
       </c>
@@ -2044,51 +2250,95 @@
       <c r="E11" s="10">
         <v>100</v>
       </c>
-      <c r="F11" s="10"/>
+      <c r="F11" s="10">
+        <v>100</v>
+      </c>
       <c r="G11" s="10">
+        <v>100</v>
+      </c>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10">
+        <v>1</v>
+      </c>
+      <c r="K11" s="10">
+        <v>5</v>
+      </c>
+      <c r="L11" s="10">
+        <v>100</v>
+      </c>
+      <c r="M11" s="2">
+        <f t="shared" si="0"/>
+        <v>106</v>
+      </c>
+      <c r="N11" s="2">
+        <v>52</v>
+      </c>
+      <c r="O11" s="2">
         <v>81</v>
       </c>
-      <c r="H11" s="10">
-        <v>1</v>
-      </c>
-      <c r="I11" s="10">
-        <v>52</v>
-      </c>
-      <c r="J11" s="10">
-        <v>81</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-    </row>
-    <row r="12" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P11" s="2">
+        <f t="shared" si="1"/>
+        <v>133</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>62.5</v>
+      </c>
+      <c r="R11" s="2">
+        <f t="shared" si="2"/>
+        <v>73.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="31" t="s">
         <v>44</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>45</v>
       </c>
       <c r="D12" s="10"/>
-      <c r="E12" s="10">
+      <c r="E12" s="34">
         <v>33</v>
       </c>
-      <c r="F12" s="10"/>
+      <c r="F12" s="10">
+        <v>73</v>
+      </c>
       <c r="G12" s="10">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="H12" s="10"/>
-      <c r="I12" s="10">
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="M12" s="2">
+        <f t="shared" si="0"/>
+        <v>66.400000000000006</v>
+      </c>
+      <c r="N12" s="2">
         <v>11</v>
       </c>
-      <c r="J12" s="10">
+      <c r="O12" s="2">
         <v>92</v>
       </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-    </row>
-    <row r="13" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P12" s="2">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="Q12" s="33">
+        <v>29</v>
+      </c>
+      <c r="R12" s="2">
+        <f t="shared" si="2"/>
+        <v>40.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
         <v>46</v>
       </c>
@@ -2102,21 +2352,42 @@
       <c r="E13" s="10">
         <v>67</v>
       </c>
-      <c r="F13" s="10"/>
+      <c r="F13" s="10">
+        <v>87</v>
+      </c>
       <c r="G13" s="10">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="H13" s="10"/>
-      <c r="I13" s="10">
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10">
+        <v>83.199999999999989</v>
+      </c>
+      <c r="M13" s="2">
+        <f t="shared" si="0"/>
+        <v>83.199999999999989</v>
+      </c>
+      <c r="N13" s="2">
         <v>22</v>
       </c>
-      <c r="J13" s="10">
+      <c r="O13" s="2">
         <v>76</v>
       </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-    </row>
-    <row r="14" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P13" s="2">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>60</v>
+      </c>
+      <c r="R13" s="2">
+        <f t="shared" si="2"/>
+        <v>66.959999999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
         <v>49</v>
       </c>
@@ -2130,21 +2401,42 @@
       <c r="E14" s="10">
         <v>89</v>
       </c>
-      <c r="F14" s="10"/>
+      <c r="F14" s="10">
+        <v>95</v>
+      </c>
       <c r="G14" s="10">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="H14" s="10"/>
-      <c r="I14" s="10">
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10">
+        <v>94.2</v>
+      </c>
+      <c r="M14" s="2">
+        <f t="shared" si="0"/>
+        <v>94.2</v>
+      </c>
+      <c r="N14" s="2">
         <v>26</v>
       </c>
-      <c r="J14" s="10">
+      <c r="O14" s="2">
         <v>85</v>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-    </row>
-    <row r="15" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P14" s="2">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>83.5</v>
+      </c>
+      <c r="R14" s="2">
+        <f t="shared" si="2"/>
+        <v>86.71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
         <v>52</v>
       </c>
@@ -2158,51 +2450,95 @@
       <c r="E15" s="10">
         <v>100</v>
       </c>
-      <c r="F15" s="10"/>
+      <c r="F15" s="10">
+        <v>100</v>
+      </c>
       <c r="G15" s="10">
-        <v>81</v>
-      </c>
-      <c r="H15" s="10">
+        <v>100</v>
+      </c>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10">
         <v>3</v>
       </c>
-      <c r="I15" s="10">
+      <c r="K15" s="10">
+        <v>5</v>
+      </c>
+      <c r="L15" s="10">
+        <v>100</v>
+      </c>
+      <c r="M15" s="2">
+        <f t="shared" si="0"/>
+        <v>108</v>
+      </c>
+      <c r="N15" s="2">
         <v>62</v>
       </c>
-      <c r="J15" s="10">
+      <c r="O15" s="2">
         <v>95</v>
       </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-    </row>
-    <row r="16" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P15" s="2">
+        <f t="shared" si="1"/>
+        <v>157</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>53</v>
+      </c>
+      <c r="R15" s="2">
+        <f t="shared" si="2"/>
+        <v>67.099999999999994</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="31" t="s">
         <v>56</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D16" s="10"/>
-      <c r="E16" s="10">
+      <c r="E16" s="34">
         <v>44</v>
       </c>
-      <c r="F16" s="10"/>
+      <c r="F16" s="10">
+        <v>70</v>
+      </c>
       <c r="G16" s="10">
         <v>81</v>
       </c>
       <c r="H16" s="10"/>
-      <c r="I16" s="10">
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="M16" s="2">
+        <f t="shared" si="0"/>
+        <v>64.400000000000006</v>
+      </c>
+      <c r="N16" s="2">
         <v>-2</v>
       </c>
-      <c r="J16" s="10">
+      <c r="O16" s="2">
         <v>0</v>
       </c>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-    </row>
-    <row r="17" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P16" s="2">
+        <f t="shared" si="1"/>
+        <v>-2</v>
+      </c>
+      <c r="Q16" s="33">
+        <v>44</v>
+      </c>
+      <c r="R16" s="2">
+        <f t="shared" si="2"/>
+        <v>50.12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
         <v>58</v>
       </c>
@@ -2216,21 +2552,42 @@
       <c r="E17" s="10">
         <v>78</v>
       </c>
-      <c r="F17" s="10"/>
+      <c r="F17" s="10">
+        <v>81</v>
+      </c>
       <c r="G17" s="10">
         <v>81</v>
       </c>
       <c r="H17" s="10"/>
-      <c r="I17" s="10">
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="M17" s="2">
+        <f t="shared" si="0"/>
+        <v>80.099999999999994</v>
+      </c>
+      <c r="N17" s="2">
         <v>4</v>
       </c>
-      <c r="J17" s="10">
+      <c r="O17" s="2">
         <v>68</v>
       </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-    </row>
-    <row r="18" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P17" s="2">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>51.5</v>
+      </c>
+      <c r="R17" s="2">
+        <f t="shared" si="2"/>
+        <v>60.08</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7" t="s">
         <v>61</v>
       </c>
@@ -2244,49 +2601,93 @@
       <c r="E18" s="10">
         <v>78</v>
       </c>
-      <c r="F18" s="10"/>
+      <c r="F18" s="10">
+        <v>70</v>
+      </c>
       <c r="G18" s="10">
         <v>81</v>
       </c>
       <c r="H18" s="10"/>
-      <c r="I18" s="10">
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="M18" s="2">
+        <f t="shared" si="0"/>
+        <v>74.599999999999994</v>
+      </c>
+      <c r="N18" s="2">
         <v>10</v>
       </c>
-      <c r="J18" s="31">
+      <c r="O18" s="42">
         <v>0</v>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-    </row>
-    <row r="19" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P18" s="2">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="Q18" s="33">
+        <v>40</v>
+      </c>
+      <c r="R18" s="2">
+        <f t="shared" si="2"/>
+        <v>50.379999999999995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="7" t="s">
         <v>64</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="36" t="s">
         <v>66</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10">
         <v>100</v>
       </c>
-      <c r="F19" s="10"/>
+      <c r="F19" s="10">
+        <v>80</v>
+      </c>
       <c r="G19" s="10">
         <v>81</v>
       </c>
       <c r="H19" s="10"/>
-      <c r="I19" s="10">
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10">
+        <v>5</v>
+      </c>
+      <c r="L19" s="10">
+        <v>91.2</v>
+      </c>
+      <c r="M19" s="2">
+        <f t="shared" si="0"/>
+        <v>91.2</v>
+      </c>
+      <c r="N19" s="2">
         <v>74</v>
       </c>
-      <c r="J19" s="10">
+      <c r="O19" s="2">
         <v>0</v>
       </c>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-    </row>
-    <row r="20" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P19" s="2">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="Q19" s="33">
+        <v>38.5</v>
+      </c>
+      <c r="R19" s="2">
+        <f t="shared" si="2"/>
+        <v>54.31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="7" t="s">
         <v>67</v>
       </c>
@@ -2300,21 +2701,42 @@
       <c r="E20" s="10">
         <v>78</v>
       </c>
-      <c r="F20" s="10"/>
+      <c r="F20" s="10">
+        <v>73</v>
+      </c>
       <c r="G20" s="10">
         <v>81</v>
       </c>
       <c r="H20" s="10"/>
-      <c r="I20" s="10">
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="M20" s="2">
+        <f t="shared" si="0"/>
+        <v>76.099999999999994</v>
+      </c>
+      <c r="N20" s="2">
         <v>51</v>
       </c>
-      <c r="J20" s="10">
+      <c r="O20" s="2">
         <v>0</v>
       </c>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-    </row>
-    <row r="21" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P20" s="2">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="Q20" s="33">
+        <v>27.5</v>
+      </c>
+      <c r="R20" s="2">
+        <f t="shared" si="2"/>
+        <v>42.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="7" t="s">
         <v>70</v>
       </c>
@@ -2328,27 +2750,50 @@
       <c r="E21" s="10">
         <v>100</v>
       </c>
-      <c r="F21" s="10"/>
+      <c r="F21" s="10">
+        <v>100</v>
+      </c>
       <c r="G21" s="10">
-        <v>81</v>
-      </c>
-      <c r="H21" s="10">
+        <v>100</v>
+      </c>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10">
         <v>4</v>
       </c>
-      <c r="I21" s="10">
+      <c r="K21" s="10">
+        <v>5</v>
+      </c>
+      <c r="L21" s="10">
+        <v>100</v>
+      </c>
+      <c r="M21" s="2">
+        <f t="shared" si="0"/>
+        <v>109</v>
+      </c>
+      <c r="N21" s="2">
         <v>73</v>
       </c>
-      <c r="J21" s="10">
+      <c r="O21" s="2">
         <v>91</v>
       </c>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-    </row>
-    <row r="22" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P21" s="2">
+        <f t="shared" si="1"/>
+        <v>164</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>65</v>
+      </c>
+      <c r="R21" s="2">
+        <f t="shared" si="2"/>
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="35" t="s">
         <v>74</v>
       </c>
       <c r="C22" s="9" t="s">
@@ -2358,21 +2803,42 @@
       <c r="E22" s="10">
         <v>67</v>
       </c>
-      <c r="F22" s="10"/>
+      <c r="F22" s="10">
+        <v>96</v>
+      </c>
       <c r="G22" s="10">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="H22" s="10"/>
-      <c r="I22" s="10">
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10">
+        <v>88.1</v>
+      </c>
+      <c r="M22" s="2">
+        <f t="shared" si="0"/>
+        <v>88.1</v>
+      </c>
+      <c r="N22" s="2">
         <v>16</v>
       </c>
-      <c r="J22" s="10">
+      <c r="O22" s="2">
         <v>96</v>
       </c>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-    </row>
-    <row r="23" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P22" s="2">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+      <c r="Q22" s="33">
+        <v>32.5</v>
+      </c>
+      <c r="R22" s="2">
+        <f t="shared" si="2"/>
+        <v>49.179999999999993</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="7" t="s">
         <v>76</v>
       </c>
@@ -2386,21 +2852,42 @@
       <c r="E23" s="10">
         <v>89</v>
       </c>
-      <c r="F23" s="10"/>
+      <c r="F23" s="10">
+        <v>87</v>
+      </c>
       <c r="G23" s="10">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="H23" s="10"/>
-      <c r="I23" s="10">
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10">
+        <v>89.600000000000009</v>
+      </c>
+      <c r="M23" s="2">
+        <f t="shared" si="0"/>
+        <v>89.600000000000009</v>
+      </c>
+      <c r="N23" s="2">
         <v>0</v>
       </c>
-      <c r="J23" s="10">
+      <c r="O23" s="2">
         <v>97</v>
       </c>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-    </row>
-    <row r="24" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P23" s="2">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>72</v>
+      </c>
+      <c r="R23" s="2">
+        <f t="shared" si="2"/>
+        <v>77.28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="7" t="s">
         <v>79</v>
       </c>
@@ -2414,21 +2901,42 @@
       <c r="E24" s="10">
         <v>78</v>
       </c>
-      <c r="F24" s="10"/>
+      <c r="F24" s="10">
+        <v>85</v>
+      </c>
       <c r="G24" s="10">
         <v>81</v>
       </c>
       <c r="H24" s="10"/>
-      <c r="I24" s="10">
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10">
+        <v>82.100000000000009</v>
+      </c>
+      <c r="M24" s="2">
+        <f t="shared" si="0"/>
+        <v>82.100000000000009</v>
+      </c>
+      <c r="N24" s="2">
         <v>12</v>
       </c>
-      <c r="J24" s="31">
+      <c r="O24" s="42">
         <v>0</v>
       </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-    </row>
-    <row r="25" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P24" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>55</v>
+      </c>
+      <c r="R24" s="2">
+        <f t="shared" si="2"/>
+        <v>63.13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="7" t="s">
         <v>82</v>
       </c>
@@ -2442,23 +2950,46 @@
       <c r="E25" s="10">
         <v>100</v>
       </c>
-      <c r="F25" s="10"/>
+      <c r="F25" s="10">
+        <v>100</v>
+      </c>
       <c r="G25" s="10">
-        <v>81</v>
-      </c>
-      <c r="H25" s="10">
+        <v>100</v>
+      </c>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10">
         <v>7</v>
       </c>
-      <c r="I25" s="10">
+      <c r="K25" s="10">
+        <v>5</v>
+      </c>
+      <c r="L25" s="10">
+        <v>100</v>
+      </c>
+      <c r="M25" s="2">
+        <f t="shared" si="0"/>
+        <v>112</v>
+      </c>
+      <c r="N25" s="2">
         <v>80</v>
       </c>
-      <c r="J25" s="10">
-        <v>100</v>
-      </c>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-    </row>
-    <row r="26" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O25" s="2">
+        <v>100</v>
+      </c>
+      <c r="P25" s="2">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>48</v>
+      </c>
+      <c r="R25" s="2">
+        <f t="shared" si="2"/>
+        <v>63.599999999999994</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="7" t="s">
         <v>85</v>
       </c>
@@ -2472,49 +3003,91 @@
       <c r="E26" s="10">
         <v>89</v>
       </c>
-      <c r="F26" s="10"/>
+      <c r="F26" s="10">
+        <v>75</v>
+      </c>
       <c r="G26" s="10">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H26" s="10"/>
-      <c r="I26" s="10">
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10">
+        <v>83</v>
+      </c>
+      <c r="M26" s="2">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+      <c r="N26" s="2">
         <v>6</v>
       </c>
-      <c r="J26" s="10">
+      <c r="O26" s="2">
         <v>88</v>
       </c>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-    </row>
-    <row r="27" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P26" s="2">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="Q26" s="33">
+        <v>36.5</v>
+      </c>
+      <c r="R26" s="2">
+        <f t="shared" si="2"/>
+        <v>50.449999999999996</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="30" t="s">
+      <c r="B27" s="31" t="s">
         <v>89</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>90</v>
       </c>
       <c r="D27" s="10"/>
-      <c r="E27" s="10">
+      <c r="E27" s="34">
         <v>56</v>
       </c>
-      <c r="F27" s="10"/>
+      <c r="F27" s="10">
+        <v>81</v>
+      </c>
       <c r="G27" s="10">
         <v>81</v>
       </c>
       <c r="H27" s="10"/>
-      <c r="I27" s="10">
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10">
+        <v>73.5</v>
+      </c>
+      <c r="M27" s="2">
+        <f t="shared" si="0"/>
+        <v>73.5</v>
+      </c>
+      <c r="N27" s="2">
         <v>6</v>
       </c>
-      <c r="J27" s="31">
+      <c r="O27" s="42">
         <v>0</v>
       </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-    </row>
-    <row r="28" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P27" s="2">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>61.5</v>
+      </c>
+      <c r="R27" s="2">
+        <f t="shared" si="2"/>
+        <v>65.099999999999994</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="7" t="s">
         <v>91</v>
       </c>
@@ -2528,21 +3101,42 @@
       <c r="E28" s="10">
         <v>67</v>
       </c>
-      <c r="F28" s="10"/>
+      <c r="F28" s="10">
+        <v>85</v>
+      </c>
       <c r="G28" s="10">
         <v>81</v>
       </c>
       <c r="H28" s="10"/>
-      <c r="I28" s="10">
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10">
+        <v>78.8</v>
+      </c>
+      <c r="M28" s="2">
+        <f t="shared" si="0"/>
+        <v>78.8</v>
+      </c>
+      <c r="N28" s="2">
         <v>1</v>
       </c>
-      <c r="J28" s="10">
+      <c r="O28" s="2">
         <v>0</v>
       </c>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-    </row>
-    <row r="29" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P28" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>67.5</v>
+      </c>
+      <c r="R28" s="2">
+        <f t="shared" si="2"/>
+        <v>70.89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="7" t="s">
         <v>94</v>
       </c>
@@ -2556,21 +3150,44 @@
       <c r="E29" s="10">
         <v>100</v>
       </c>
-      <c r="F29" s="10"/>
+      <c r="F29" s="10">
+        <v>70</v>
+      </c>
       <c r="G29" s="10">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H29" s="10"/>
-      <c r="I29" s="10">
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10">
+        <v>5</v>
+      </c>
+      <c r="L29" s="10">
+        <v>88.8</v>
+      </c>
+      <c r="M29" s="2">
+        <f t="shared" si="0"/>
+        <v>88.8</v>
+      </c>
+      <c r="N29" s="2">
         <v>2</v>
       </c>
-      <c r="J29" s="10">
+      <c r="O29" s="2">
         <v>92</v>
       </c>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-    </row>
-    <row r="30" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P29" s="2">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>53.5</v>
+      </c>
+      <c r="R29" s="2">
+        <f t="shared" si="2"/>
+        <v>64.089999999999989</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="7" t="s">
         <v>97</v>
       </c>
@@ -2584,23 +3201,44 @@
       <c r="E30" s="10">
         <v>67</v>
       </c>
-      <c r="F30" s="10"/>
+      <c r="F30" s="10">
+        <v>81</v>
+      </c>
       <c r="G30" s="10">
         <v>81</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10">
         <v>1</v>
       </c>
-      <c r="I30" s="10">
+      <c r="K30" s="10"/>
+      <c r="L30" s="10">
+        <v>77.8</v>
+      </c>
+      <c r="M30" s="2">
+        <f t="shared" si="0"/>
+        <v>77.8</v>
+      </c>
+      <c r="N30" s="2">
         <v>28</v>
       </c>
-      <c r="J30" s="10">
+      <c r="O30" s="2">
         <v>0</v>
       </c>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-    </row>
-    <row r="31" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P30" s="2">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>63</v>
+      </c>
+      <c r="R30" s="2">
+        <f t="shared" si="2"/>
+        <v>67.44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="7" t="s">
         <v>100</v>
       </c>
@@ -2614,21 +3252,42 @@
       <c r="E31" s="10">
         <v>89</v>
       </c>
-      <c r="F31" s="10"/>
+      <c r="F31" s="10">
+        <v>0</v>
+      </c>
       <c r="G31" s="10">
         <v>81</v>
       </c>
       <c r="H31" s="10"/>
-      <c r="I31" s="10">
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10">
+        <v>42.9</v>
+      </c>
+      <c r="M31" s="2">
+        <f t="shared" si="0"/>
+        <v>42.9</v>
+      </c>
+      <c r="N31" s="2">
         <v>0</v>
       </c>
-      <c r="J31" s="31">
+      <c r="O31" s="42">
         <v>0</v>
       </c>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-    </row>
-    <row r="32" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P31" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>70.5</v>
+      </c>
+      <c r="R31" s="2">
+        <f t="shared" si="2"/>
+        <v>62.219999999999992</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7" t="s">
         <v>103</v>
       </c>
@@ -2642,23 +3301,46 @@
       <c r="E32" s="10">
         <v>100</v>
       </c>
-      <c r="F32" s="10"/>
+      <c r="F32" s="10">
+        <v>100</v>
+      </c>
       <c r="G32" s="10">
-        <v>81</v>
-      </c>
-      <c r="H32" s="10">
+        <v>100</v>
+      </c>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10">
         <v>1</v>
       </c>
-      <c r="I32" s="10">
+      <c r="K32" s="10">
+        <v>5</v>
+      </c>
+      <c r="L32" s="10">
+        <v>100</v>
+      </c>
+      <c r="M32" s="2">
+        <f t="shared" si="0"/>
+        <v>106</v>
+      </c>
+      <c r="N32" s="2">
         <v>48</v>
       </c>
-      <c r="J32" s="10">
+      <c r="O32" s="2">
         <v>94</v>
       </c>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-    </row>
-    <row r="33" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P32" s="2">
+        <f t="shared" si="1"/>
+        <v>142</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>67</v>
+      </c>
+      <c r="R32" s="2">
+        <f t="shared" si="2"/>
+        <v>76.900000000000006</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="7" t="s">
         <v>106</v>
       </c>
@@ -2672,21 +3354,44 @@
       <c r="E33" s="10">
         <v>100</v>
       </c>
-      <c r="F33" s="10"/>
+      <c r="F33" s="10">
+        <v>96</v>
+      </c>
       <c r="G33" s="10">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="H33" s="10"/>
-      <c r="I33" s="10">
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10">
+        <v>5</v>
+      </c>
+      <c r="L33" s="10">
+        <v>100</v>
+      </c>
+      <c r="M33" s="2">
+        <f t="shared" si="0"/>
+        <v>103</v>
+      </c>
+      <c r="N33" s="2">
         <v>18</v>
       </c>
-      <c r="J33" s="10">
+      <c r="O33" s="2">
         <v>91</v>
       </c>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-    </row>
-    <row r="34" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P33" s="2">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>67.5</v>
+      </c>
+      <c r="R33" s="2">
+        <f t="shared" si="2"/>
+        <v>77.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="7" t="s">
         <v>109</v>
       </c>
@@ -2700,21 +3405,42 @@
       <c r="E34" s="10">
         <v>78</v>
       </c>
-      <c r="F34" s="10"/>
+      <c r="F34" s="10">
+        <v>97</v>
+      </c>
       <c r="G34" s="10">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="H34" s="10"/>
-      <c r="I34" s="10">
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10">
+        <v>91.9</v>
+      </c>
+      <c r="M34" s="2">
+        <f t="shared" si="0"/>
+        <v>91.9</v>
+      </c>
+      <c r="N34" s="2">
         <v>14</v>
       </c>
-      <c r="J34" s="10">
+      <c r="O34" s="2">
         <v>95</v>
       </c>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-    </row>
-    <row r="35" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P34" s="2">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="Q34" s="33">
+        <v>55</v>
+      </c>
+      <c r="R34" s="2">
+        <f t="shared" si="2"/>
+        <v>66.069999999999993</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="7" t="s">
         <v>112</v>
       </c>
@@ -2728,23 +3454,46 @@
       <c r="E35" s="10">
         <v>100</v>
       </c>
-      <c r="F35" s="10"/>
+      <c r="F35" s="10">
+        <v>100</v>
+      </c>
       <c r="G35" s="10">
-        <v>81</v>
-      </c>
-      <c r="H35" s="10">
+        <v>100</v>
+      </c>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10">
         <v>1</v>
       </c>
-      <c r="I35" s="10">
+      <c r="K35" s="10">
+        <v>5</v>
+      </c>
+      <c r="L35" s="10">
+        <v>100</v>
+      </c>
+      <c r="M35" s="2">
+        <f t="shared" si="0"/>
+        <v>106</v>
+      </c>
+      <c r="N35" s="2">
         <v>70</v>
       </c>
-      <c r="J35" s="10">
+      <c r="O35" s="2">
         <v>86</v>
       </c>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-    </row>
-    <row r="36" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P35" s="2">
+        <f t="shared" si="1"/>
+        <v>156</v>
+      </c>
+      <c r="Q35" s="33">
+        <v>58</v>
+      </c>
+      <c r="R35" s="2">
+        <f t="shared" si="2"/>
+        <v>70.599999999999994</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="7" t="s">
         <v>115</v>
       </c>
@@ -2758,23 +3507,46 @@
       <c r="E36" s="10">
         <v>100</v>
       </c>
-      <c r="F36" s="10"/>
+      <c r="F36" s="10">
+        <v>100</v>
+      </c>
       <c r="G36" s="10">
-        <v>81</v>
-      </c>
-      <c r="H36" s="10">
+        <v>100</v>
+      </c>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10">
         <v>1</v>
       </c>
-      <c r="I36" s="10">
+      <c r="K36" s="10">
+        <v>5</v>
+      </c>
+      <c r="L36" s="10">
+        <v>100</v>
+      </c>
+      <c r="M36" s="2">
+        <f t="shared" si="0"/>
+        <v>106</v>
+      </c>
+      <c r="N36" s="2">
         <v>56</v>
       </c>
-      <c r="J36" s="10">
+      <c r="O36" s="2">
         <v>62</v>
       </c>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-    </row>
-    <row r="37" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P36" s="2">
+        <f t="shared" si="1"/>
+        <v>118</v>
+      </c>
+      <c r="Q36" s="33">
+        <v>51</v>
+      </c>
+      <c r="R36" s="2">
+        <f t="shared" si="2"/>
+        <v>65.699999999999989</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="7" t="s">
         <v>118</v>
       </c>
@@ -2788,49 +3560,93 @@
       <c r="E37" s="10">
         <v>100</v>
       </c>
-      <c r="F37" s="10"/>
+      <c r="F37" s="10">
+        <v>100</v>
+      </c>
       <c r="G37" s="10">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="H37" s="10"/>
-      <c r="I37" s="10">
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10">
+        <v>5</v>
+      </c>
+      <c r="L37" s="10">
+        <v>100</v>
+      </c>
+      <c r="M37" s="2">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="N37" s="2">
         <v>60</v>
       </c>
-      <c r="J37" s="10">
+      <c r="O37" s="2">
         <v>95</v>
       </c>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-    </row>
-    <row r="38" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P37" s="2">
+        <f t="shared" si="1"/>
+        <v>155</v>
+      </c>
+      <c r="Q37" s="33">
+        <v>54.5</v>
+      </c>
+      <c r="R37" s="2">
+        <f t="shared" si="2"/>
+        <v>68.150000000000006</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="7" t="s">
         <v>121</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" s="32" t="s">
         <v>123</v>
       </c>
       <c r="D38" s="10"/>
-      <c r="E38" s="10">
-        <v>56</v>
-      </c>
-      <c r="F38" s="10"/>
+      <c r="E38" s="34">
+        <v>100</v>
+      </c>
+      <c r="F38" s="10">
+        <v>90</v>
+      </c>
       <c r="G38" s="10">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="H38" s="10"/>
-      <c r="I38" s="10">
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10">
+        <v>95</v>
+      </c>
+      <c r="M38" s="2">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="N38" s="2">
         <v>12</v>
       </c>
-      <c r="J38" s="10">
+      <c r="O38" s="2">
         <v>92</v>
       </c>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-    </row>
-    <row r="39" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P38" s="2">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="Q38" s="33">
+        <v>45</v>
+      </c>
+      <c r="R38" s="42">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="7" t="s">
         <v>124</v>
       </c>
@@ -2844,23 +3660,44 @@
       <c r="E39" s="10">
         <v>78</v>
       </c>
-      <c r="F39" s="10"/>
+      <c r="F39" s="10">
+        <v>98</v>
+      </c>
       <c r="G39" s="10">
-        <v>81</v>
-      </c>
-      <c r="H39" s="10">
+        <v>100</v>
+      </c>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10">
         <v>1</v>
       </c>
-      <c r="I39" s="10">
+      <c r="K39" s="10"/>
+      <c r="L39" s="10">
+        <v>93.4</v>
+      </c>
+      <c r="M39" s="2">
+        <f t="shared" si="0"/>
+        <v>93.4</v>
+      </c>
+      <c r="N39" s="2">
         <v>16</v>
       </c>
-      <c r="J39" s="10">
+      <c r="O39" s="2">
         <v>97</v>
       </c>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-    </row>
-    <row r="40" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P39" s="2">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="Q39" s="33">
+        <v>54.5</v>
+      </c>
+      <c r="R39" s="2">
+        <f t="shared" si="2"/>
+        <v>66.17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="7" t="s">
         <v>127</v>
       </c>
@@ -2874,21 +3711,42 @@
       <c r="E40" s="10">
         <v>67</v>
       </c>
-      <c r="F40" s="10"/>
+      <c r="F40" s="10">
+        <v>70</v>
+      </c>
       <c r="G40" s="10">
         <v>81</v>
       </c>
       <c r="H40" s="10"/>
-      <c r="I40" s="10">
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10">
+        <v>71.3</v>
+      </c>
+      <c r="M40" s="2">
+        <f t="shared" si="0"/>
+        <v>71.3</v>
+      </c>
+      <c r="N40" s="2">
         <v>4</v>
       </c>
-      <c r="J40" s="10">
+      <c r="O40" s="2">
         <v>27</v>
       </c>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-    </row>
-    <row r="41" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P40" s="2">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="Q40" s="33">
+        <v>40.5</v>
+      </c>
+      <c r="R40" s="2">
+        <f t="shared" si="2"/>
+        <v>49.739999999999995</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="7" t="s">
         <v>130</v>
       </c>
@@ -2902,23 +3760,46 @@
       <c r="E41" s="10">
         <v>100</v>
       </c>
-      <c r="F41" s="10"/>
+      <c r="F41" s="10">
+        <v>86</v>
+      </c>
       <c r="G41" s="10">
         <v>81</v>
       </c>
-      <c r="H41" s="10">
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10">
         <v>4</v>
       </c>
-      <c r="I41" s="10">
+      <c r="K41" s="10">
+        <v>5</v>
+      </c>
+      <c r="L41" s="10">
+        <v>98.2</v>
+      </c>
+      <c r="M41" s="2">
+        <f t="shared" si="0"/>
+        <v>98.2</v>
+      </c>
+      <c r="N41" s="2">
         <v>46</v>
       </c>
-      <c r="J41" s="10">
+      <c r="O41" s="2">
         <v>0</v>
       </c>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-    </row>
-    <row r="42" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P41" s="2">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="Q41" s="33">
+        <v>49</v>
+      </c>
+      <c r="R41" s="2">
+        <f t="shared" si="2"/>
+        <v>63.76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="7" t="s">
         <v>133</v>
       </c>
@@ -2932,23 +3813,44 @@
       <c r="E42" s="10">
         <v>89</v>
       </c>
-      <c r="F42" s="10"/>
+      <c r="F42" s="10">
+        <v>100</v>
+      </c>
       <c r="G42" s="10">
-        <v>81</v>
-      </c>
-      <c r="H42" s="10">
+        <v>100</v>
+      </c>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10">
         <v>1</v>
       </c>
-      <c r="I42" s="10">
+      <c r="K42" s="10"/>
+      <c r="L42" s="10">
+        <v>97.7</v>
+      </c>
+      <c r="M42" s="2">
+        <f t="shared" si="0"/>
+        <v>97.7</v>
+      </c>
+      <c r="N42" s="2">
         <v>68</v>
       </c>
-      <c r="J42" s="10">
+      <c r="O42" s="2">
         <v>97</v>
       </c>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-    </row>
-    <row r="43" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P42" s="2">
+        <f t="shared" si="1"/>
+        <v>165</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>87</v>
+      </c>
+      <c r="R42" s="2">
+        <f t="shared" si="2"/>
+        <v>90.21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="7" t="s">
         <v>136</v>
       </c>
@@ -2962,21 +3864,42 @@
       <c r="E43" s="10">
         <v>78</v>
       </c>
-      <c r="F43" s="10"/>
+      <c r="F43" s="10">
+        <v>88</v>
+      </c>
       <c r="G43" s="10">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="H43" s="10"/>
-      <c r="I43" s="10">
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10">
+        <v>86.4</v>
+      </c>
+      <c r="M43" s="2">
+        <f t="shared" si="0"/>
+        <v>86.4</v>
+      </c>
+      <c r="N43" s="2">
         <v>36</v>
       </c>
-      <c r="J43" s="10">
+      <c r="O43" s="2">
         <v>95</v>
       </c>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-    </row>
-    <row r="44" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P43" s="2">
+        <f t="shared" si="1"/>
+        <v>131</v>
+      </c>
+      <c r="Q43" s="2">
+        <v>66</v>
+      </c>
+      <c r="R43" s="2">
+        <f t="shared" si="2"/>
+        <v>72.12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="7" t="s">
         <v>139</v>
       </c>
@@ -2988,23 +3911,44 @@
       </c>
       <c r="D44" s="10"/>
       <c r="E44" s="10">
-        <v>78</v>
-      </c>
-      <c r="F44" s="10"/>
+        <v>67</v>
+      </c>
+      <c r="F44" s="10">
+        <v>88</v>
+      </c>
       <c r="G44" s="10">
         <v>81</v>
       </c>
       <c r="H44" s="10"/>
-      <c r="I44" s="10">
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10">
+        <v>80.3</v>
+      </c>
+      <c r="M44" s="2">
+        <f t="shared" si="0"/>
+        <v>80.3</v>
+      </c>
+      <c r="N44" s="2">
         <v>44</v>
       </c>
-      <c r="J44" s="10">
+      <c r="O44" s="2">
         <v>90</v>
       </c>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-    </row>
-    <row r="45" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P44" s="2">
+        <f t="shared" si="1"/>
+        <v>134</v>
+      </c>
+      <c r="Q44" s="2">
+        <v>72</v>
+      </c>
+      <c r="R44" s="2">
+        <f t="shared" si="2"/>
+        <v>74.489999999999995</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="7" t="s">
         <v>142</v>
       </c>
@@ -3018,21 +3962,42 @@
       <c r="E45" s="10">
         <v>67</v>
       </c>
-      <c r="F45" s="10"/>
+      <c r="F45" s="10">
+        <v>82</v>
+      </c>
       <c r="G45" s="10">
         <v>81</v>
       </c>
       <c r="H45" s="10"/>
-      <c r="I45" s="10">
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10">
+        <v>77.3</v>
+      </c>
+      <c r="M45" s="2">
+        <f t="shared" si="0"/>
+        <v>77.3</v>
+      </c>
+      <c r="N45" s="2">
         <v>30</v>
       </c>
-      <c r="J45" s="10">
+      <c r="O45" s="2">
         <v>0</v>
       </c>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-    </row>
-    <row r="46" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P45" s="2">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>57</v>
+      </c>
+      <c r="R45" s="2">
+        <f t="shared" si="2"/>
+        <v>63.089999999999996</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7" t="s">
         <v>145</v>
       </c>
@@ -3046,23 +4011,46 @@
       <c r="E46" s="10">
         <v>100</v>
       </c>
-      <c r="F46" s="10"/>
+      <c r="F46" s="10">
+        <v>100</v>
+      </c>
       <c r="G46" s="10">
-        <v>81</v>
-      </c>
-      <c r="H46" s="10">
+        <v>100</v>
+      </c>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10">
         <v>3</v>
       </c>
-      <c r="I46" s="10">
+      <c r="K46" s="10">
+        <v>5</v>
+      </c>
+      <c r="L46" s="10">
+        <v>100</v>
+      </c>
+      <c r="M46" s="2">
+        <f t="shared" si="0"/>
+        <v>108</v>
+      </c>
+      <c r="N46" s="2">
         <v>75</v>
       </c>
-      <c r="J46" s="10">
+      <c r="O46" s="2">
         <v>96</v>
       </c>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-    </row>
-    <row r="47" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P46" s="2">
+        <f t="shared" si="1"/>
+        <v>171</v>
+      </c>
+      <c r="Q46" s="2">
+        <v>64.5</v>
+      </c>
+      <c r="R46" s="2">
+        <f t="shared" si="2"/>
+        <v>75.150000000000006</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="7" t="s">
         <v>148</v>
       </c>
@@ -3076,21 +4064,44 @@
       <c r="E47" s="10">
         <v>100</v>
       </c>
-      <c r="F47" s="10"/>
+      <c r="F47" s="10">
+        <v>94</v>
+      </c>
       <c r="G47" s="10">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="H47" s="10"/>
-      <c r="I47" s="10">
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10">
+        <v>5</v>
+      </c>
+      <c r="L47" s="10">
+        <v>100</v>
+      </c>
+      <c r="M47" s="2">
+        <f t="shared" si="0"/>
+        <v>102</v>
+      </c>
+      <c r="N47" s="2">
         <v>19</v>
       </c>
-      <c r="J47" s="10">
+      <c r="O47" s="2">
         <v>90</v>
       </c>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-    </row>
-    <row r="48" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P47" s="2">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="Q47" s="2">
+        <v>46</v>
+      </c>
+      <c r="R47" s="2">
+        <f t="shared" si="2"/>
+        <v>62.199999999999996</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="7" t="s">
         <v>151</v>
       </c>
@@ -3104,187 +4115,266 @@
       <c r="E48" s="10">
         <v>67</v>
       </c>
-      <c r="F48" s="10"/>
+      <c r="F48" s="10">
+        <v>70</v>
+      </c>
       <c r="G48" s="10">
         <v>81</v>
       </c>
       <c r="H48" s="10"/>
-      <c r="I48" s="10">
+      <c r="I48" s="10"/>
+      <c r="J48" s="28"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10">
+        <v>71.3</v>
+      </c>
+      <c r="M48" s="2">
+        <f t="shared" si="0"/>
+        <v>71.3</v>
+      </c>
+      <c r="N48" s="2">
         <v>1</v>
       </c>
-      <c r="J48" s="31">
+      <c r="O48" s="42">
         <v>0</v>
       </c>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-    </row>
-    <row r="49" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="7" t="s">
+      <c r="P48" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>55.5</v>
+      </c>
+      <c r="R48" s="2">
+        <f t="shared" si="2"/>
+        <v>60.239999999999995</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="43" t="s">
         <v>154</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="37" t="s">
         <v>156</v>
       </c>
       <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-    </row>
-    <row r="50" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="33" t="s">
+      <c r="E49" s="34">
+        <v>60</v>
+      </c>
+      <c r="F49" s="34">
+        <v>60</v>
+      </c>
+      <c r="G49" s="34">
+        <v>60</v>
+      </c>
+      <c r="H49" s="34"/>
+      <c r="I49" s="34"/>
+      <c r="J49" s="34"/>
+      <c r="K49" s="34"/>
+      <c r="L49" s="34">
+        <v>60</v>
+      </c>
+      <c r="M49" s="33"/>
+      <c r="N49" s="33"/>
+      <c r="O49" s="33"/>
+      <c r="Q49" s="2">
+        <v>44.5</v>
+      </c>
+      <c r="R49" s="2">
+        <f t="shared" si="2"/>
+        <v>49.15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R50" s="2"/>
+    </row>
+    <row r="51" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B51" s="33"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="33"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="33"/>
-      <c r="H51" s="33"/>
-      <c r="I51" s="33"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="33"/>
-      <c r="L51" s="33"/>
-      <c r="M51" s="33"/>
-    </row>
-    <row r="52" spans="1:13" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="34" t="s">
+      <c r="B51" s="63"/>
+      <c r="C51" s="63"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="63"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="63"/>
+      <c r="I51" s="63"/>
+      <c r="J51" s="63"/>
+      <c r="K51" s="63"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="63"/>
+      <c r="O51" s="63"/>
+      <c r="P51" s="63"/>
+      <c r="R51" s="2"/>
+    </row>
+    <row r="52" spans="1:18" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="B52" s="34"/>
-      <c r="C52" s="34"/>
-      <c r="D52" s="35" t="s">
+      <c r="B52" s="61"/>
+      <c r="C52" s="61"/>
+      <c r="D52" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="E52" s="35"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="35" t="s">
+      <c r="E52" s="62"/>
+      <c r="F52" s="62"/>
+      <c r="G52" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="H52" s="35"/>
-      <c r="I52" s="35"/>
-      <c r="J52" s="35" t="s">
+      <c r="H52" s="62"/>
+      <c r="I52" s="62"/>
+      <c r="J52" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="K52" s="35"/>
-      <c r="L52" s="35"/>
-      <c r="M52" s="19"/>
-    </row>
-    <row r="53" spans="1:13" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="32" t="s">
+      <c r="K52" s="62"/>
+      <c r="L52" s="62"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="19"/>
+      <c r="R52" s="2"/>
+    </row>
+    <row r="53" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B53" s="39" t="s">
+      <c r="B53" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="40" t="s">
+      <c r="C53" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="D53" s="38" t="s">
+      <c r="D53" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="38"/>
-      <c r="I53" s="38"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="38"/>
-      <c r="L53" s="36" t="s">
+      <c r="E53" s="56"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="56"/>
+      <c r="J53" s="56"/>
+      <c r="K53" s="56"/>
+      <c r="L53" s="50" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="32"/>
-      <c r="B54" s="39"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="41" t="s">
+      <c r="M53" s="38"/>
+      <c r="N53" s="38"/>
+      <c r="O53" s="38"/>
+    </row>
+    <row r="54" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="57"/>
+      <c r="B54" s="58"/>
+      <c r="C54" s="59"/>
+      <c r="D54" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="E54" s="41" t="s">
+      <c r="E54" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="F54" s="41" t="s">
+      <c r="F54" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="G54" s="41" t="s">
+      <c r="G54" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="H54" s="41"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="36"/>
-    </row>
-    <row r="55" spans="1:13" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="32"/>
-      <c r="B55" s="39"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="41"/>
-      <c r="I55" s="41"/>
-      <c r="J55" s="41"/>
-      <c r="K55" s="41"/>
-      <c r="L55" s="36"/>
-    </row>
-    <row r="56" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="7" t="s">
+      <c r="H54" s="49"/>
+      <c r="I54" s="49"/>
+      <c r="J54" s="49"/>
+      <c r="K54" s="49"/>
+      <c r="L54" s="50"/>
+      <c r="M54" s="38"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="38"/>
+    </row>
+    <row r="55" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="57"/>
+      <c r="B55" s="58"/>
+      <c r="C55" s="59"/>
+      <c r="D55" s="49"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
+      <c r="H55" s="49"/>
+      <c r="I55" s="49"/>
+      <c r="J55" s="49"/>
+      <c r="K55" s="49"/>
+      <c r="L55" s="50"/>
+      <c r="M55" s="38"/>
+      <c r="N55" s="38"/>
+      <c r="O55" s="38"/>
+    </row>
+    <row r="56" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="C56" s="28" t="s">
-        <v>160</v>
+      <c r="C56" s="37" t="s">
+        <v>159</v>
       </c>
       <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-    </row>
-    <row r="57" spans="1:13" s="3" customFormat="1" ht="12" x14ac:dyDescent="0.15">
+      <c r="E56" s="34">
+        <v>60</v>
+      </c>
+      <c r="F56" s="34">
+        <v>60</v>
+      </c>
+      <c r="G56" s="34">
+        <v>60</v>
+      </c>
+      <c r="H56" s="34"/>
+      <c r="I56" s="34"/>
+      <c r="J56" s="34"/>
+      <c r="K56" s="34"/>
+      <c r="L56" s="34">
+        <v>60</v>
+      </c>
+      <c r="M56" s="33"/>
+      <c r="N56" s="33"/>
+      <c r="O56" s="33"/>
+      <c r="Q56" s="2">
+        <v>63</v>
+      </c>
+      <c r="R56" s="2">
+        <f t="shared" si="2"/>
+        <v>62.099999999999994</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" s="3" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="B57" s="11"/>
       <c r="C57" s="12"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A58" s="46" t="s">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A58" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="46"/>
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="46"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="46"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="46"/>
-      <c r="K58" s="46"/>
-      <c r="L58" s="46"/>
-      <c r="M58" s="20"/>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A59" s="47" t="s">
+      <c r="B58" s="51"/>
+      <c r="C58" s="51"/>
+      <c r="D58" s="51"/>
+      <c r="E58" s="51"/>
+      <c r="F58" s="51"/>
+      <c r="G58" s="51"/>
+      <c r="H58" s="51"/>
+      <c r="I58" s="51"/>
+      <c r="J58" s="51"/>
+      <c r="K58" s="51"/>
+      <c r="L58" s="51"/>
+      <c r="M58" s="29"/>
+      <c r="N58" s="29"/>
+      <c r="O58" s="29"/>
+      <c r="P58" s="20"/>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A59" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="B59" s="48"/>
+      <c r="B59" s="53"/>
       <c r="C59" s="6" t="s">
         <v>12</v>
       </c>
@@ -3300,37 +4390,43 @@
       <c r="G59" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H59" s="47" t="s">
+      <c r="H59" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="I59" s="49"/>
-      <c r="J59" s="48"/>
-      <c r="K59" s="50" t="s">
+      <c r="I59" s="54"/>
+      <c r="J59" s="53"/>
+      <c r="K59" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="L59" s="50"/>
-      <c r="M59" s="21"/>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A60" s="42"/>
-      <c r="B60" s="42"/>
+      <c r="L59" s="55"/>
+      <c r="M59" s="39"/>
+      <c r="N59" s="39"/>
+      <c r="O59" s="39"/>
+      <c r="P59" s="21"/>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A60" s="45"/>
+      <c r="B60" s="45"/>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
       <c r="E60" s="13"/>
       <c r="F60" s="14"/>
       <c r="G60" s="14"/>
-      <c r="H60" s="43"/>
-      <c r="I60" s="44"/>
-      <c r="J60" s="45"/>
-      <c r="K60" s="42"/>
-      <c r="L60" s="42"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="H60" s="46"/>
+      <c r="I60" s="47"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="45"/>
+      <c r="L60" s="45"/>
+      <c r="M60" s="40"/>
+      <c r="N60" s="40"/>
+      <c r="O60" s="40"/>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.15">
       <c r="B61" s="24"/>
       <c r="C61" s="25"/>
       <c r="D61" s="26"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.15">
       <c r="B63" s="15" t="s">
         <v>19</v>
       </c>
@@ -3344,10 +4440,39 @@
       <c r="K63" s="22"/>
       <c r="L63" s="22"/>
       <c r="M63" s="23"/>
+      <c r="N63" s="23"/>
+      <c r="O63" s="23"/>
+      <c r="P63" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="A51:P51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D3:K3"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="K4:K5"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="H60:J60"/>
     <mergeCell ref="K60:L60"/>
@@ -3363,35 +4488,14 @@
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="C53:C55"/>
     <mergeCell ref="D54:D55"/>
-    <mergeCell ref="C3:C5"/>
     <mergeCell ref="F54:F55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="A51:M51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="J52:L52"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D3:K3"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
+  <conditionalFormatting sqref="R6:R49">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>60</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.10972222222222222" right="0.10972222222222222" top="0.38124999999999998" bottom="0.5" header="0.38124999999999998" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <rowBreaks count="1" manualBreakCount="1">

--- a/network/file/成绩登分册-6.xlsx
+++ b/network/file/成绩登分册-6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\network\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A70B27-B48B-49C1-BBA4-14268037AC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FBA784-3CF9-41F7-B423-2E8717668A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7894F757-77BE-43E5-A7F7-5BED1F0CA09B}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="168">
   <si>
     <t>广州华立学院学生平时成绩登记表</t>
   </si>
@@ -530,6 +530,10 @@
   </si>
   <si>
     <t>平时累计</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
@@ -537,7 +541,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -729,6 +733,13 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFC00000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1256,7 +1267,7 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1366,6 +1377,36 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1378,12 +1419,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1399,28 +1434,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1840,81 +1854,79 @@
     <col min="1" max="1" width="4.375" customWidth="1"/>
     <col min="2" max="2" width="11.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="11.625" style="5" customWidth="1"/>
-    <col min="4" max="11" width="7.25" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="7.875" customWidth="1"/>
-    <col min="13" max="15" width="7.875" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="8" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="9" customWidth="1"/>
-    <col min="18" max="18" width="0" hidden="1" customWidth="1"/>
+    <col min="4" max="11" width="7.25" customWidth="1"/>
+    <col min="12" max="15" width="7.875" customWidth="1"/>
+    <col min="16" max="16" width="8" customWidth="1"/>
+    <col min="17" max="18" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
+      <c r="A1" s="64" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
       <c r="M1" s="44"/>
       <c r="N1" s="44"/>
       <c r="O1" s="44"/>
       <c r="P1" s="44"/>
     </row>
     <row r="2" spans="1:18" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="62" t="s">
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62" t="s">
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
       <c r="M2" s="30"/>
       <c r="N2" s="30"/>
       <c r="O2" s="30"/>
       <c r="P2" s="19"/>
     </row>
     <row r="3" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="56" t="s">
+      <c r="D3" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="50" t="s">
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="51" t="s">
         <v>5</v>
       </c>
       <c r="M3" s="38"/>
@@ -1922,30 +1934,30 @@
       <c r="O3" s="38"/>
     </row>
     <row r="4" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="57"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="57" t="s">
+      <c r="A4" s="47"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="57" t="s">
+      <c r="E4" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="57" t="s">
+      <c r="F4" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="57" t="s">
+      <c r="G4" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60" t="s">
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="60" t="s">
+      <c r="K4" s="46" t="s">
         <v>163</v>
       </c>
-      <c r="L4" s="50"/>
+      <c r="L4" s="51"/>
       <c r="M4" s="38"/>
       <c r="N4" s="38"/>
       <c r="O4" s="38"/>
@@ -1954,18 +1966,18 @@
       </c>
     </row>
     <row r="5" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="57"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="50"/>
+      <c r="A5" s="47"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="51"/>
       <c r="M5" s="38"/>
       <c r="N5" s="41" t="s">
         <v>164</v>
@@ -4192,47 +4204,47 @@
       <c r="R50" s="2"/>
     </row>
     <row r="51" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="63" t="s">
+      <c r="A51" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B51" s="63"/>
-      <c r="C51" s="63"/>
-      <c r="D51" s="63"/>
-      <c r="E51" s="63"/>
-      <c r="F51" s="63"/>
-      <c r="G51" s="63"/>
-      <c r="H51" s="63"/>
-      <c r="I51" s="63"/>
-      <c r="J51" s="63"/>
-      <c r="K51" s="63"/>
-      <c r="L51" s="63"/>
-      <c r="M51" s="63"/>
-      <c r="N51" s="63"/>
-      <c r="O51" s="63"/>
-      <c r="P51" s="63"/>
+      <c r="B51" s="48"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+      <c r="I51" s="48"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="48"/>
+      <c r="L51" s="48"/>
+      <c r="M51" s="48"/>
+      <c r="N51" s="48"/>
+      <c r="O51" s="48"/>
+      <c r="P51" s="48"/>
       <c r="R51" s="2"/>
     </row>
     <row r="52" spans="1:18" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="61" t="s">
+      <c r="A52" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="B52" s="61"/>
-      <c r="C52" s="61"/>
-      <c r="D52" s="62" t="s">
+      <c r="B52" s="49"/>
+      <c r="C52" s="49"/>
+      <c r="D52" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="E52" s="62"/>
-      <c r="F52" s="62"/>
-      <c r="G52" s="62" t="s">
+      <c r="E52" s="50"/>
+      <c r="F52" s="50"/>
+      <c r="G52" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="H52" s="62"/>
-      <c r="I52" s="62"/>
-      <c r="J52" s="62" t="s">
+      <c r="H52" s="50"/>
+      <c r="I52" s="50"/>
+      <c r="J52" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="K52" s="62"/>
-      <c r="L52" s="62"/>
+      <c r="K52" s="50"/>
+      <c r="L52" s="50"/>
       <c r="M52" s="30"/>
       <c r="N52" s="30"/>
       <c r="O52" s="30"/>
@@ -4240,26 +4252,26 @@
       <c r="R52" s="2"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="57" t="s">
+      <c r="A53" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B53" s="58" t="s">
+      <c r="B53" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="59" t="s">
+      <c r="C53" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D53" s="56" t="s">
+      <c r="D53" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="E53" s="56"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
-      <c r="H53" s="56"/>
-      <c r="I53" s="56"/>
-      <c r="J53" s="56"/>
-      <c r="K53" s="56"/>
-      <c r="L53" s="50" t="s">
+      <c r="E53" s="52"/>
+      <c r="F53" s="52"/>
+      <c r="G53" s="52"/>
+      <c r="H53" s="52"/>
+      <c r="I53" s="52"/>
+      <c r="J53" s="52"/>
+      <c r="K53" s="52"/>
+      <c r="L53" s="51" t="s">
         <v>5</v>
       </c>
       <c r="M53" s="38"/>
@@ -4267,43 +4279,43 @@
       <c r="O53" s="38"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="57"/>
-      <c r="B54" s="58"/>
-      <c r="C54" s="59"/>
-      <c r="D54" s="49" t="s">
+      <c r="A54" s="47"/>
+      <c r="B54" s="53"/>
+      <c r="C54" s="54"/>
+      <c r="D54" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="E54" s="49" t="s">
+      <c r="E54" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="F54" s="49" t="s">
+      <c r="F54" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G54" s="49" t="s">
+      <c r="G54" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="H54" s="49"/>
-      <c r="I54" s="49"/>
-      <c r="J54" s="49"/>
-      <c r="K54" s="49"/>
-      <c r="L54" s="50"/>
+      <c r="H54" s="45"/>
+      <c r="I54" s="45"/>
+      <c r="J54" s="45"/>
+      <c r="K54" s="45"/>
+      <c r="L54" s="51"/>
       <c r="M54" s="38"/>
       <c r="N54" s="38"/>
       <c r="O54" s="38"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="57"/>
-      <c r="B55" s="58"/>
-      <c r="C55" s="59"/>
-      <c r="D55" s="49"/>
-      <c r="E55" s="49"/>
-      <c r="F55" s="49"/>
-      <c r="G55" s="49"/>
-      <c r="H55" s="49"/>
-      <c r="I55" s="49"/>
-      <c r="J55" s="49"/>
-      <c r="K55" s="49"/>
-      <c r="L55" s="50"/>
+      <c r="A55" s="47"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="45"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="45"/>
+      <c r="G55" s="45"/>
+      <c r="H55" s="45"/>
+      <c r="I55" s="45"/>
+      <c r="J55" s="45"/>
+      <c r="K55" s="45"/>
+      <c r="L55" s="51"/>
       <c r="M55" s="38"/>
       <c r="N55" s="38"/>
       <c r="O55" s="38"/>
@@ -4351,30 +4363,30 @@
       <c r="C57" s="12"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A58" s="51" t="s">
+      <c r="A58" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="51"/>
-      <c r="C58" s="51"/>
-      <c r="D58" s="51"/>
-      <c r="E58" s="51"/>
-      <c r="F58" s="51"/>
-      <c r="G58" s="51"/>
-      <c r="H58" s="51"/>
-      <c r="I58" s="51"/>
-      <c r="J58" s="51"/>
-      <c r="K58" s="51"/>
-      <c r="L58" s="51"/>
+      <c r="B58" s="59"/>
+      <c r="C58" s="59"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="59"/>
+      <c r="F58" s="59"/>
+      <c r="G58" s="59"/>
+      <c r="H58" s="59"/>
+      <c r="I58" s="59"/>
+      <c r="J58" s="59"/>
+      <c r="K58" s="59"/>
+      <c r="L58" s="59"/>
       <c r="M58" s="29"/>
       <c r="N58" s="29"/>
       <c r="O58" s="29"/>
       <c r="P58" s="20"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A59" s="52" t="s">
+      <c r="A59" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="B59" s="53"/>
+      <c r="B59" s="61"/>
       <c r="C59" s="6" t="s">
         <v>12</v>
       </c>
@@ -4390,33 +4402,33 @@
       <c r="G59" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H59" s="52" t="s">
+      <c r="H59" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="I59" s="54"/>
-      <c r="J59" s="53"/>
-      <c r="K59" s="55" t="s">
+      <c r="I59" s="62"/>
+      <c r="J59" s="61"/>
+      <c r="K59" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="L59" s="55"/>
+      <c r="L59" s="63"/>
       <c r="M59" s="39"/>
       <c r="N59" s="39"/>
       <c r="O59" s="39"/>
       <c r="P59" s="21"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A60" s="45"/>
-      <c r="B60" s="45"/>
+      <c r="A60" s="55"/>
+      <c r="B60" s="55"/>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
       <c r="E60" s="13"/>
       <c r="F60" s="14"/>
       <c r="G60" s="14"/>
-      <c r="H60" s="46"/>
-      <c r="I60" s="47"/>
-      <c r="J60" s="48"/>
-      <c r="K60" s="45"/>
-      <c r="L60" s="45"/>
+      <c r="H60" s="56"/>
+      <c r="I60" s="57"/>
+      <c r="J60" s="58"/>
+      <c r="K60" s="55"/>
+      <c r="L60" s="55"/>
       <c r="M60" s="40"/>
       <c r="N60" s="40"/>
       <c r="O60" s="40"/>
@@ -4446,6 +4458,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="H60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="L53:L55"/>
+    <mergeCell ref="A58:L58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="K59:L59"/>
+    <mergeCell ref="D53:K53"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="G54:G55"/>
     <mergeCell ref="H54:H55"/>
     <mergeCell ref="I54:I55"/>
@@ -4462,33 +4501,6 @@
     <mergeCell ref="D3:K3"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="H60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="J54:J55"/>
-    <mergeCell ref="K54:K55"/>
-    <mergeCell ref="L53:L55"/>
-    <mergeCell ref="A58:L58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="K59:L59"/>
-    <mergeCell ref="D53:K53"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="F54:F55"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <conditionalFormatting sqref="R6:R49">
